--- a/travel/2026_보홀.xlsx
+++ b/travel/2026_보홀.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tool\여행\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huj11\Desktop\집\csw\travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9136204B-0BC0-4BBE-9B33-C8F84C9D61F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2325D67F-8582-4E67-AFAB-C746C5F499AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
-    <sheet name="예산" sheetId="2" r:id="rId2"/>
+    <sheet name="예산" sheetId="4" r:id="rId2"/>
     <sheet name="예약" sheetId="3" r:id="rId3"/>
+    <sheet name="숙소후보" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
   <si>
     <t>토</t>
   </si>
@@ -67,22 +68,6 @@
     <t>금</t>
   </si>
   <si>
-    <t>2:15 인천 출발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:20 보홀 도착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20:25 보홀 출발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>05:20 인천 도착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>세종 출발</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,32 +76,163 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>세종 도착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>항목</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YJ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>합계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>항공권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>페소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비행기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅁ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보홀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마닐라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 보홀 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노스 젠 풀빌라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/north-zen-villas_2/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1922887&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=edd99c7b-e980-40d6-819a-b024ee42f43d&amp;tspTypes=8&amp;los=3&amp;searchrequestid=d3694ff4-393a-4442-a2ea-8f320551a3b2&amp;ds=kWMJcJq5dYGYeGG8</t>
+  </si>
+  <si>
+    <t>호핑투어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발리카삭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안경원숭이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나팔링투어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반딧불</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스쿠버(교육 코스 좋은데로)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부겐빌리아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤난리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갈릭앤레몬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>토토에페피노(x)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aftertaste Food house</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팡라오씨 리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리조트 포인트에서 정어리떼 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 노스젠빌라 선셋 및 반딧불이 투어</t>
+  </si>
+  <si>
+    <r>
+      <t>2. 나팔링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 스쿠버다이빙 체험 + 히낙다난 동굴</t>
+    </r>
+  </si>
+  <si>
+    <t>3. 발리카삭 호핑투어 (돌고래. 거북이)</t>
+  </si>
+  <si>
+    <t>4. 육상투어(성당.로복강.맨메이드숲.안경원숭이.초콜릿언덕)</t>
+  </si>
+  <si>
+    <r>
+      <t>[출처]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Dotum"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 필리핀 보홀 자유여행 총정리ㅡ여행일정.비용.맛집.날씨.추천 마사지샵 내돈내산|</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Dotum"/>
+        <family val="3"/>
+      </rPr>
+      <t>작성자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Dotum"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 앵두윤정</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -124,10 +240,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="178" formatCode="&quot;₩&quot;#,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,8 +268,48 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="휴먼엑스포"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF141414"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Dotum"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Dotum"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,8 +322,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -191,7 +377,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -207,53 +395,135 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -263,65 +533,99 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -747,110 +1051,119 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F97559-E962-4670-8971-A738245E3ABD}">
-  <dimension ref="B2:M28"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M50"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="7"/>
-      <c r="C2" s="12" t="s">
+    <row r="1" spans="1:13" ht="45.75">
+      <c r="A1" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="B2" s="5"/>
+      <c r="C2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="17.25" thickBot="1">
       <c r="B3" s="2"/>
-      <c r="C3" s="13">
+      <c r="C3" s="11">
         <v>46235</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="11">
         <v>46236</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="11">
         <v>46237</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="11">
         <v>46238</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="11">
         <v>46239</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="11">
         <v>46240</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="11">
         <v>46241</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="11">
         <v>46242</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="11">
         <v>46243</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="14">
+    <row r="4" spans="1:13">
+      <c r="B4" s="12">
         <v>0</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="8"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="14">
+      <c r="K4" s="23">
+        <v>0.50694444444444442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5" s="12">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="8"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="14">
+      <c r="K5" s="24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="12">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="8" t="s">
-        <v>8</v>
+      <c r="C6" s="8"/>
+      <c r="D6" s="27">
+        <v>9.375E-2</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -858,131 +1171,138 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="14">
+    </row>
+    <row r="7" spans="1:13">
+      <c r="B7" s="12">
         <v>0.125</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="24" t="s">
+        <v>18</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="14">
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="12">
         <v>0.16666666666666699</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="8"/>
+      <c r="C8" s="8"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="8"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="14">
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9" s="12">
         <v>0.20833333333333301</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="25">
+        <v>0.2361111111111111</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="14">
+      <c r="K9" s="25">
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17.25" thickBot="1">
+      <c r="B10" s="12">
         <v>0.25</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="26" t="s">
+        <v>17</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="14">
+      <c r="K10" s="26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11" s="12">
         <v>0.29166666666666702</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="14">
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:13" ht="17.25" thickBot="1">
+      <c r="B12" s="12">
         <v>0.33333333333333298</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="14">
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="B13" s="12">
         <v>0.375</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="23">
+        <v>0.39930555555555558</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="14">
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14" s="12">
         <v>0.41666666666666702</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="24" t="s">
+        <v>17</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B15" s="14">
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="B15" s="12">
         <v>0.45833333333333298</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="8" t="s">
-        <v>9</v>
+      <c r="C15" s="8"/>
+      <c r="D15" s="25">
+        <v>0.47222222222222221</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -990,27 +1310,29 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="14">
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:13" ht="17.25" thickBot="1">
+      <c r="B16" s="12">
         <v>0.5</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="3"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="26" t="s">
+        <v>16</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="8"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="14">
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="12">
         <v>0.54166666666666696</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="8"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1018,13 +1340,13 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="8"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="14">
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="12">
         <v>0.58333333333333304</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="8"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1032,13 +1354,13 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="14">
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="12">
         <v>0.625</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="8"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1046,13 +1368,13 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="14">
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="12">
         <v>0.66666666666666696</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="8"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1060,13 +1382,13 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="14">
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="12">
         <v>0.70833333333333304</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="8"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1074,13 +1396,13 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="8"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="14">
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" s="12">
         <v>0.75</v>
       </c>
-      <c r="C22" s="10"/>
+      <c r="C22" s="8"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1088,13 +1410,13 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="8"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B23" s="14">
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="2:11" ht="17.25" thickBot="1">
+      <c r="B23" s="12">
         <v>0.79166666666666696</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="8"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -1102,59 +1424,63 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="8"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="14">
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="12">
         <v>0.83333333333333304</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>12</v>
+      <c r="C24" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="J24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="K24" s="8"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="14">
+      <c r="J24" s="23">
+        <v>0.85069444444444442</v>
+      </c>
+      <c r="K24" s="6"/>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25" s="12">
         <v>0.875</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="8"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B26" s="14">
+      <c r="J25" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="6"/>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="12">
         <v>0.91666666666666696</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="8"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B27" s="14">
+      <c r="J26" s="25">
+        <v>0.92013888888888884</v>
+      </c>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="2:11" ht="17.25" thickBot="1">
+      <c r="B27" s="12">
         <v>0.95833333333333304</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>13</v>
+      <c r="C27" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1162,22 +1488,112 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B28" s="15">
+      <c r="J27" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="13">
         <v>1</v>
       </c>
-      <c r="C28" s="11"/>
+      <c r="C28" s="9"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="C31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="C32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9">
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9">
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9">
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9">
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9">
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9">
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9">
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="3:9" ht="36">
+      <c r="D46" s="30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9" ht="36">
+      <c r="D47" s="31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="3:9" ht="36">
+      <c r="D48" s="30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4" ht="54">
+      <c r="D49" s="30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" ht="33.75">
+      <c r="D50" s="32" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1186,400 +1602,171 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA70EDAC-428A-4D76-907D-5BE4F6C8EB53}">
-  <dimension ref="B2:E43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B29DE7-3267-4196-8A3E-54333E9A8DE2}">
+  <dimension ref="B2:F20"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="5" width="21.5" customWidth="1"/>
+    <col min="1" max="1" width="4.125" customWidth="1"/>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="20">
-        <v>948000</v>
-      </c>
-      <c r="E3" s="17">
-        <f>SUM(C3,D3)</f>
-        <v>948000</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="3"/>
+    <row r="2" spans="2:6">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="16">
+        <v>985619</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17"/>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="15"/>
       <c r="C4" s="16"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="17">
-        <f t="shared" ref="E4:E43" si="0">SUM(C4,D4)</f>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="17"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="17"/>
+    </row>
+    <row r="19" spans="2:6" ht="17.25" thickBot="1">
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="17"/>
+    </row>
+    <row r="20" spans="2:6" ht="17.25" thickBot="1">
+      <c r="B20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="21">
+        <f>SUM(C3:C19)</f>
+        <v>985619</v>
+      </c>
+      <c r="D20" s="21">
+        <f t="shared" ref="D20:E20" si="0">SUM(D3:D19)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="3"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="17">
+      <c r="E20" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="3"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="3"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="3"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="3"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="3"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="3"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="3"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="3"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="3"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="3"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="3"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="3"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="3"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="3"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="3"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="3"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="3"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="3"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="3"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="3"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="3"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="3"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="3"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="3"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="3"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="3"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="3"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="3"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="3"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="3"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="3"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="3"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="3"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B42" s="3"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="F20" s="22">
+        <f>SUM(C20:E20)</f>
+        <v>985619</v>
       </c>
     </row>
   </sheetData>
@@ -1591,10 +1778,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4CB3F24-E440-4CFB-AA49-9CEA408CE6AD}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78285AA-8DCF-418C-B5C5-79E1E3F6D2B4}">
+  <dimension ref="C3:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="3" max="3" width="26.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5">
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="29">
+        <v>166640</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/travel/2026_보홀.xlsx
+++ b/travel/2026_보홀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huj11\Desktop\집\csw\travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2325D67F-8582-4E67-AFAB-C746C5F499AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A9EEA6-1E63-413F-A98F-2A3E5354D8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>토</t>
   </si>
@@ -234,6 +234,140 @@
       <t xml:space="preserve"> 앵두윤정</t>
     </r>
   </si>
+  <si>
+    <t>리조트캉스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6박9일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌라 카사디아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아미한 리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바탈라 리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/batala-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/amihan-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=7%2C9%2C8&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>미티 리조트 앤 스파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/mithi-resort-and-spa/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=0fe1414e-6e90-4934-9730-2ecc15aadec6&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>시내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호캉스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/villa-kasadya/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>헤난 타왈라 리조트 보홀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/henann-tawala-resort-bohol/hotel/tagbilaran-city-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=8&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>르유 호텔 알로나 팡라오 (LEUX HOTEL Alona Panglao)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/leux-hotel_2/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>위치깡패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤난 리조트 알로나 비치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/henann-resort-alona-beach/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=-1&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>헤난 프리미어 코스트 리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/henann-premier-coast-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=15%2C-1&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/casa-mannis-garden/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=3&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>알로나 오스트리아 리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후기가넘좋음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alona Apartments</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/alona-apartments_2/hotel/all/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=1&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>넓음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갬성지림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">옐로우 망고 리조트 보홀 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/yellow-mango-resort-bohol/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=9&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+  </si>
+  <si>
+    <t>알로나 골든 팜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/alona-golden-palm/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/bird-of-paradise/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버드 오브 파라다이스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아모리타 리조트 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.agoda.com/ko-kr/amorita-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=a20b728c-5956-4ad1-b992-9d05007db2ba&amp;ds=UvZQ9QXraVhKf83X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -243,7 +377,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,6 +442,24 @@
       <name val="Dotum"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -353,7 +505,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -514,16 +666,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -623,10 +809,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1062,6 +1264,9 @@
       <c r="A1" s="28" t="s">
         <v>19</v>
       </c>
+      <c r="D1" s="36" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="2" spans="1:13">
       <c r="B2" s="5"/>
@@ -1502,9 +1707,11 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="7"/>
+      <c r="H28" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" s="34"/>
+      <c r="J28" s="35"/>
       <c r="K28" s="7"/>
     </row>
     <row r="31" spans="2:11">
@@ -1596,6 +1803,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H28:J28"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1788,13 +1998,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78285AA-8DCF-418C-B5C5-79E1E3F6D2B4}">
-  <dimension ref="C3:E3"/>
+  <dimension ref="C2:K20"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="26.5" customWidth="1"/>
+    <col min="8" max="8" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5">
+    <row r="2" spans="3:11">
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="3:11">
       <c r="C3" t="s">
         <v>20</v>
       </c>
@@ -1804,9 +2023,177 @@
       <c r="E3" t="s">
         <v>21</v>
       </c>
+      <c r="H3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3">
+        <v>118730</v>
+      </c>
+      <c r="J3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="3:11">
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4">
+        <v>251349</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4">
+        <v>73378</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11">
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5">
+        <v>138083</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11">
+      <c r="H6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6">
+        <v>50353</v>
+      </c>
+      <c r="J6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11">
+      <c r="H7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7">
+        <v>104787</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11">
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8">
+        <v>141342</v>
+      </c>
+      <c r="J8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11">
+      <c r="H9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9">
+        <v>64817</v>
+      </c>
+      <c r="J9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11">
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10">
+        <v>118334</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11">
+      <c r="H11" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11">
+        <v>135723</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17">
+        <v>195095</v>
+      </c>
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5">
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18">
+        <v>236914</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5">
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19">
+        <v>233015</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5">
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20">
+        <v>234338</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E19" r:id="rId1" display="https://www.agoda.com/ko-kr/henann-premier-coast-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=15%2C-1&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X" xr:uid="{802DDE39-9D6A-4D84-9555-9EEDFA775322}"/>
+    <hyperlink ref="J10" r:id="rId2" display="https://www.agoda.com/ko-kr/alona-golden-palm/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X" xr:uid="{D7B23464-54A0-4469-A333-03D360F50729}"/>
+    <hyperlink ref="J11" r:id="rId3" display="https://www.agoda.com/ko-kr/bird-of-paradise/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X" xr:uid="{B3119F92-D8F2-4F88-8A90-0D76A0728BE3}"/>
+    <hyperlink ref="E20" r:id="rId4" display="https://www.agoda.com/ko-kr/amorita-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=a20b728c-5956-4ad1-b992-9d05007db2ba&amp;ds=UvZQ9QXraVhKf83X" xr:uid="{F5F4D0CF-24FC-4FBD-9854-E4A6B16B981F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/travel/2026_보홀.xlsx
+++ b/travel/2026_보홀.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huj11\Desktop\집\csw\travel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A9EEA6-1E63-413F-A98F-2A3E5354D8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE8E73B-70AD-4275-8459-8B5904A9B817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="예약" sheetId="3" r:id="rId3"/>
     <sheet name="숙소후보" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숙소후보!$B$2:$R$2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
   <si>
     <t>토</t>
   </si>
@@ -118,9 +121,6 @@
   <si>
     <t>노스 젠 풀빌라</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.agoda.com/ko-kr/north-zen-villas_2/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1922887&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=edd99c7b-e980-40d6-819a-b024ee42f43d&amp;tspTypes=8&amp;los=3&amp;searchrequestid=d3694ff4-393a-4442-a2ea-8f320551a3b2&amp;ds=kWMJcJq5dYGYeGG8</t>
   </si>
   <si>
     <t>호핑투어</t>
@@ -255,19 +255,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/batala-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
-    <t>https://www.agoda.com/ko-kr/amihan-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=7%2C9%2C8&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>미티 리조트 앤 스파</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/mithi-resort-and-spa/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=0fe1414e-6e90-4934-9730-2ecc15aadec6&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>시내</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -276,23 +267,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/villa-kasadya/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>헤난 타왈라 리조트 보홀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/henann-tawala-resort-bohol/hotel/tagbilaran-city-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=8&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>르유 호텔 알로나 팡라오 (LEUX HOTEL Alona Panglao)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/leux-hotel_2/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>위치깡패</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -301,20 +283,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/henann-resort-alona-beach/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=-1&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>헤난 프리미어 코스트 리조트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/henann-premier-coast-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=15%2C-1&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.agoda.com/ko-kr/casa-mannis-garden/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=3&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>알로나 오스트리아 리조트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -327,9 +299,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/alona-apartments_2/hotel/all/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=1&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>넓음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -342,21 +311,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/yellow-mango-resort-bohol/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=9&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-  </si>
-  <si>
     <t>알로나 골든 팜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/alona-golden-palm/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.agoda.com/ko-kr/bird-of-paradise/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>버드 오브 파라다이스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -365,7 +323,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.agoda.com/ko-kr/amorita-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=a20b728c-5956-4ad1-b992-9d05007db2ba&amp;ds=UvZQ9QXraVhKf83X</t>
+    <t>가격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선순위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장 동일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -373,9 +347,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+    <numFmt numFmtId="177" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -709,7 +684,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -797,9 +772,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -809,6 +781,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -818,11 +793,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1264,8 +1242,8 @@
       <c r="A1" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="36" t="s">
-        <v>42</v>
+      <c r="D1" s="32" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1708,7 +1686,7 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="35"/>
@@ -1716,20 +1694,20 @@
     </row>
     <row r="31" spans="2:11">
       <c r="C31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="2:11">
       <c r="C32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="3:9">
       <c r="C33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I33" t="s">
         <v>15</v>
@@ -1737,69 +1715,69 @@
     </row>
     <row r="34" spans="3:9">
       <c r="C34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" t="s">
         <v>22</v>
-      </c>
-      <c r="E35" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="36" spans="3:9">
       <c r="E36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G36" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" t="s">
         <v>34</v>
-      </c>
-      <c r="H36" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="38" spans="3:9">
       <c r="D38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="3:9">
       <c r="D40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="3:9">
       <c r="D42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="3:9" ht="36">
-      <c r="D46" s="30" t="s">
+      <c r="D46" s="29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9" ht="36">
+      <c r="D47" s="30" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="3:9" ht="36">
-      <c r="D47" s="31" t="s">
+    <row r="48" spans="3:9" ht="36">
+      <c r="D48" s="29" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="3:9" ht="36">
-      <c r="D48" s="30" t="s">
+    <row r="49" spans="4:4" ht="54">
+      <c r="D49" s="29" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="4:4" ht="54">
-      <c r="D49" s="30" t="s">
+    <row r="50" spans="4:4" ht="33.75">
+      <c r="D50" s="31" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="50" spans="4:4" ht="33.75">
-      <c r="D50" s="32" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1998,201 +1976,260 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78285AA-8DCF-418C-B5C5-79E1E3F6D2B4}">
-  <dimension ref="C2:K20"/>
+  <dimension ref="B2:O11"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="3" max="3" width="26.5" customWidth="1"/>
-    <col min="8" max="8" width="19.5" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11">
-      <c r="C2" t="s">
+    <row r="2" spans="2:15">
+      <c r="B2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="38">
+        <v>166640</v>
+      </c>
+      <c r="D3" s="37"/>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="38">
+        <v>118730</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="38">
+        <v>233015</v>
+      </c>
+      <c r="N3" s="37"/>
+      <c r="O3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="38">
+        <v>251349</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="38">
+        <v>135723</v>
+      </c>
+      <c r="I4" s="37"/>
+      <c r="J4" s="2">
+        <v>2</v>
+      </c>
+      <c r="L4" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="M4" s="38">
+        <v>236914</v>
+      </c>
+      <c r="N4" s="37"/>
+      <c r="O4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="G5" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="38">
+        <v>73378</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="38">
+        <v>195095</v>
+      </c>
+      <c r="N5" s="37"/>
+      <c r="O5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="G6" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="38">
+        <v>138083</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="2">
+        <v>4</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="38">
+        <v>234338</v>
+      </c>
+      <c r="N6" s="37"/>
+      <c r="O6" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="G7" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="38">
+        <v>64817</v>
+      </c>
+      <c r="I7" s="37"/>
+      <c r="J7" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="G8" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="38">
+        <v>141342</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="G9" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="38">
+        <v>50353</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="G10" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="38">
+        <v>118334</v>
+      </c>
+      <c r="I10" s="37"/>
+      <c r="J10" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="G11" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="38">
+        <v>104787</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="3:11">
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="29">
-        <v>166640</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3">
-        <v>118730</v>
-      </c>
-      <c r="J3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="3:11">
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4">
-        <v>251349</v>
-      </c>
-      <c r="E4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4">
-        <v>73378</v>
-      </c>
-      <c r="J4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="3:11">
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5">
-        <v>138083</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="3:11">
-      <c r="H6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6">
-        <v>50353</v>
-      </c>
-      <c r="J6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="3:11">
-      <c r="H7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7">
-        <v>104787</v>
-      </c>
-      <c r="J7" t="s">
-        <v>56</v>
-      </c>
-      <c r="K7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11">
-      <c r="H8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8">
-        <v>141342</v>
-      </c>
-      <c r="J8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="3:11">
-      <c r="H9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9">
-        <v>64817</v>
-      </c>
-      <c r="J9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="3:11">
-      <c r="H10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10">
-        <v>118334</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="3:11">
-      <c r="H11" t="s">
-        <v>74</v>
-      </c>
-      <c r="I11">
-        <v>135723</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5">
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17">
-        <v>195095</v>
-      </c>
-      <c r="E17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5">
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18">
-        <v>236914</v>
-      </c>
-      <c r="E18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="3:5">
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19">
-        <v>233015</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5">
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20">
-        <v>234338</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>76</v>
+      <c r="J11" s="2">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E19" r:id="rId1" display="https://www.agoda.com/ko-kr/henann-premier-coast-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;tspTypes=15%2C-1&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X" xr:uid="{802DDE39-9D6A-4D84-9555-9EEDFA775322}"/>
-    <hyperlink ref="J10" r:id="rId2" display="https://www.agoda.com/ko-kr/alona-golden-palm/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X" xr:uid="{D7B23464-54A0-4469-A333-03D360F50729}"/>
-    <hyperlink ref="J11" r:id="rId3" display="https://www.agoda.com/ko-kr/bird-of-paradise/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=b975f157-894a-43ca-a3dc-34ffa9fb036d&amp;ds=UvZQ9QXraVhKf83X" xr:uid="{B3119F92-D8F2-4F88-8A90-0D76A0728BE3}"/>
-    <hyperlink ref="E20" r:id="rId4" display="https://www.agoda.com/ko-kr/amorita-resort/hotel/bohol-ph.html?countryId=70&amp;finalPriceView=1&amp;isShowMobileAppPrice=false&amp;cid=1729890&amp;numberOfBedrooms=&amp;familyMode=false&amp;adults=2&amp;children=0&amp;rooms=1&amp;maxRooms=0&amp;checkIn=2026-08-2&amp;isCalendarCallout=false&amp;childAges=&amp;numberOfGuest=0&amp;missingChildAges=false&amp;travellerType=1&amp;showReviewSubmissionEntry=false&amp;currencyCode=KRW&amp;isFreeOccSearch=false&amp;tag=296115503ijCfW69e62f1ae7&amp;flightSearchCriteria=%5Bobject+Object%5D&amp;los=4&amp;searchrequestid=a20b728c-5956-4ad1-b992-9d05007db2ba&amp;ds=UvZQ9QXraVhKf83X" xr:uid="{F5F4D0CF-24FC-4FBD-9854-E4A6B16B981F}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{4F8ED818-C876-40E0-B7A8-7D382605FD4C}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{A9981921-D08B-4F00-9BF5-027C6757E249}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{486AF9B7-E3F7-4F80-8394-A795B7521A54}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{437F0357-B3F7-47E9-94BF-1E41FC4B23F1}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{36D1394C-E608-4250-959E-C80191CB4E2A}"/>
+    <hyperlink ref="G9" r:id="rId6" xr:uid="{35DC177C-7860-4A2B-9AF1-C913FADC718F}"/>
+    <hyperlink ref="G11" r:id="rId7" xr:uid="{FEB89D9F-6357-4D64-B090-BCCDF822649C}"/>
+    <hyperlink ref="G8" r:id="rId8" xr:uid="{E352F777-56C3-4CD3-B75B-2B007C89ECB2}"/>
+    <hyperlink ref="G7" r:id="rId9" xr:uid="{C25CFC5E-AE56-4634-9921-CD8B8FB7C99C}"/>
+    <hyperlink ref="G10" r:id="rId10" xr:uid="{D78C6E34-3441-4580-90EC-E4C7F0BB92A0}"/>
+    <hyperlink ref="G4" r:id="rId11" xr:uid="{53457735-9D06-4D4E-B2CE-28E7ED622AC4}"/>
+    <hyperlink ref="L5" r:id="rId12" xr:uid="{E700EBCA-29E7-41D6-9FC3-20881E251C62}"/>
+    <hyperlink ref="L4" r:id="rId13" xr:uid="{9085A7AF-385D-489F-8985-F471F69F0407}"/>
+    <hyperlink ref="L3" r:id="rId14" xr:uid="{85F0D401-D82C-4701-8C9D-D1914E33212C}"/>
+    <hyperlink ref="L6" r:id="rId15" xr:uid="{301CF784-B35C-4462-B6BF-E9C6A38554A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
